--- a/INSTANCES/instances_xlsx/A_MTN_8/262FL_10A_5.xlsx
+++ b/INSTANCES/instances_xlsx/A_MTN_8/262FL_10A_5.xlsx
@@ -8671,7 +8671,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -8722,7 +8722,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>1</v>
